--- a/performance_tracking_forms/016_production_line_efficiency_evaluation_form--performance_tracking_forms.xlsx
+++ b/performance_tracking_forms/016_production_line_efficiency_evaluation_form--performance_tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'excellent',_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Excellent', 'label': 'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'good',_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Good', 'label': 'good'}</t>
+          <t>good</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'fair',_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Fair', 'label': 'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'poor',_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Poor', 'label': 'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'line_1',_'label':_'line_1'}</t>
+          <t>line_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Line 1', 'label': 'Line 1'}</t>
+          <t>Line 1</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'line_2',_'label':_'line_2'}</t>
+          <t>line_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Line 2', 'label': 'Line 2'}</t>
+          <t>Line 2</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'line_3',_'label':_'line_3'}</t>
+          <t>line_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Line 3', 'label': 'Line 3'}</t>
+          <t>Line 3</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'line_4',_'label':_'line_4'}</t>
+          <t>line_4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Line 4', 'label': 'Line 4'}</t>
+          <t>Line 4</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'line_1',_'label':_'line_1'}</t>
+          <t>line_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Line 1', 'label': 'Line 1'}</t>
+          <t>Line 1</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'line_2',_'label':_'line_2'}</t>
+          <t>line_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Line 2', 'label': 'Line 2'}</t>
+          <t>Line 2</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'line_3',_'label':_'line_3'}</t>
+          <t>line_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Line 3', 'label': 'Line 3'}</t>
+          <t>Line 3</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'line_4',_'label':_'line_4'}</t>
+          <t>line_4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Line 4', 'label': 'Line 4'}</t>
+          <t>Line 4</t>
         </is>
       </c>
     </row>
